--- a/offer-prices_fin.xlsx
+++ b/offer-prices_fin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Monastyrska\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216A1F53-21E4-4680-A1CA-A6B22AACF4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AFF996-1B9E-4C8C-B221-43BDD92692AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30795" yWindow="-570" windowWidth="29145" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="10" windowWidth="19430" windowHeight="10310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
   <si>
     <t>external_Id</t>
   </si>
@@ -58,9 +58,6 @@
     <t>xlsxoffSourse</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>xlsxoff_Sourse2</t>
   </si>
   <si>
@@ -74,6 +71,72 @@
   </si>
   <si>
     <t>2000.00</t>
+  </si>
+  <si>
+    <t>xlsxoff_Sourse1</t>
+  </si>
+  <si>
+    <t>358.00</t>
+  </si>
+  <si>
+    <t>copy_xlsxoff_Sourse2</t>
+  </si>
+  <si>
+    <t>csvoffSourse</t>
+  </si>
+  <si>
+    <t>csvoffcopy_Soursedelete1-Qatest1s</t>
+  </si>
+  <si>
+    <t>csvoff_Sourse1</t>
+  </si>
+  <si>
+    <t>mp1882709</t>
+  </si>
+  <si>
+    <t>1567.00</t>
+  </si>
+  <si>
+    <t>700.00</t>
+  </si>
+  <si>
+    <t>csvoff_Sourse2</t>
+  </si>
+  <si>
+    <t>copy_csvoffSourse</t>
+  </si>
+  <si>
+    <t>copy_csvoffcopy_Soursedelete1-Qatest1s</t>
+  </si>
+  <si>
+    <t>copy_csvoff_Sourse1</t>
+  </si>
+  <si>
+    <t>copy_csvoff_Sourse2</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
 </sst>
 </file>
@@ -422,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.36328125" style="1" customWidth="1"/>
@@ -469,46 +532,193 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F8"/>
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
